--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/17062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/17062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miércoles, 17 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Mateo
-Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
-*Oración de la mañana*
-Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
-Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
-Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
-En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>miércoles, 17 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 1-6. 16-18 En aquel tiempo, Jesús dijo a sus discípulos: “Tengan cuidado de no practicar sus obras de piedad delante de los hombres para que los vean. De lo contrario, no tendrán recompensa con su Padre celestial. Por lo tanto, cuando des limosna, no lo anuncies con trompeta, como hacen los hipócritas en las sinagogas y por las calles, para que los alaben los hombres. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando des limosna, que no sepa tu mano izquierda lo que hace la derecha, para que tu limosna quede en secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes hagan oración, no sean como los hipócritas, a quienes les gusta orar de pie en las sinagogas y en las esquinas de las plazas, para que los vea la gente. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando vayas a orar, entra en tu cuarto, cierra la puerta y ora ante tu Padre, que está allí, en lo secreto; y tu Padre, que ve lo secreto, te recompensará. Cuando ustedes ayunen, no pongan cara triste, como esos hipócritas que descuidan la apariencia de su rostro, para que la gente note que están ayunando. Yo les aseguro que ya recibieron su recompensa. Tú, en cambio, cuando ayunes, perfúmate la cabeza y lávate la cara, para que no sepa la gente que estás ayunando, sino tu Padre, que está en lo secreto; y tu Padre, que ve lo secreto, te recompensará’’.
+*Oración de la mañana*
+Querido Jesús, en este nuevo día, ayúdame a seguir tus enseñanzas y a realizar mis actos de piedad con genuinidad y humildad. Que no busque la aprobación de los hombres, sino que, en todo, busque agradarte a Ti, consciente de que mi recompensa está en el cielo y no en los elogios humanos.
+Padre celestial, te agradezco por este nuevo amanecer, por la oportunidad de vivir y amar en tu presencia. Ayúdame a mantener mis acciones de amor y caridad en secreto, sabiendo que Tú, que ves en lo oculto, recompensarás mi sinceridad y devoción.
+Espíritu Santo, guía mis pensamientos y acciones en este día. Que mi oración sea sincera y mi ayuno sea un acto de adoración a Ti, no una exhibición para los demás. Infunde en mí la fuerza para mantener la pureza en mis intenciones, y la sabiduría para practicar la piedad sin buscar reconocimiento humano, sino únicamente tu glorificación.
+En la Trinidad Santa confío, en este y todos los días de mi vida. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>